--- a/dev_stuffs/1敌人数值投放模板.xlsx
+++ b/dev_stuffs/1敌人数值投放模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9C2BE9-0BC3-4E41-87E2-E41B89E410CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759BD7DB-DBE8-415E-8A54-FF2D3C83FE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="3510" windowWidth="30825" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-570" yWindow="3660" windowWidth="23940" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="伤害计算" sheetId="1" r:id="rId1"/>
@@ -174,6 +174,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
@@ -182,12 +183,14 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -428,14 +431,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -887,44 +890,44 @@
       <c r="L2" s="20"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="H3" s="23" t="s">
+      <c r="B3" s="21"/>
+      <c r="H3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="23"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.15">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="H4" s="23" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="H4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A5" s="24" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
       <c r="O5" s="8" t="s">
         <v>38</v>
       </c>
@@ -945,8 +948,8 @@
       <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="21"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="1" t="s">
         <v>21</v>
       </c>
@@ -993,11 +996,11 @@
       <c r="AB6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AE6" s="21" t="s">
+      <c r="AE6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="AF6" s="21"/>
-      <c r="AG6" s="21"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="22"/>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.15">
       <c r="A7" s="16">
@@ -1040,14 +1043,14 @@
         <v>3</v>
       </c>
       <c r="P7" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q7" s="13">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="R7" s="12">
         <f>(O7+P7)*Q7</f>
-        <v>9.1</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="T7" s="12">
         <v>15</v>
@@ -1123,7 +1126,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="12">
         <f>(O8+P7)*Q7</f>
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="T8" s="12">
         <v>20</v>
@@ -1192,7 +1195,7 @@
       <c r="Q9" s="7"/>
       <c r="R9" s="12">
         <f>(O9+P7)*Q7</f>
-        <v>13.299999999999999</v>
+        <v>13.600000000000001</v>
       </c>
       <c r="T9" s="12">
         <v>30</v>
@@ -1261,7 +1264,7 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="12">
         <f>(O10+P7)*Q7</f>
-        <v>15.399999999999999</v>
+        <v>16</v>
       </c>
       <c r="T10" s="12">
         <v>40</v>
@@ -1349,14 +1352,14 @@
         <v>3</v>
       </c>
       <c r="P12" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q12" s="13">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="R12" s="12">
         <f>(O12+P12)*Q12</f>
-        <v>28</v>
+        <v>24.3</v>
       </c>
       <c r="T12" s="12">
         <v>15</v>
@@ -1434,7 +1437,7 @@
       <c r="Q13" s="7"/>
       <c r="R13" s="12">
         <f>(O13+P12)*Q12</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="T13" s="12">
         <v>20</v>
@@ -1504,7 +1507,7 @@
       <c r="Q14" s="7"/>
       <c r="R14" s="12">
         <f>(O14+P12)*Q12</f>
-        <v>34</v>
+        <v>32.400000000000006</v>
       </c>
       <c r="T14" s="12">
         <v>30</v>
@@ -1574,7 +1577,7 @@
       <c r="Q15" s="7"/>
       <c r="R15" s="12">
         <f>(O15+P12)*Q12</f>
-        <v>37</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="T15" s="12">
         <v>40</v>
@@ -1661,11 +1664,15 @@
       <c r="O17" s="12">
         <v>3</v>
       </c>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="13"/>
+      <c r="P17" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>1.75</v>
+      </c>
       <c r="R17" s="12">
         <f>(O17+P17)*Q17</f>
-        <v>0</v>
+        <v>68.25</v>
       </c>
       <c r="T17" s="12">
         <v>20</v>
@@ -1742,7 +1749,7 @@
       <c r="Q18" s="7"/>
       <c r="R18" s="12">
         <f>(O18+P17)*Q17</f>
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="T18" s="12">
         <v>30</v>
@@ -1811,7 +1818,7 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="12">
         <f>(O19+P17)*Q17</f>
-        <v>0</v>
+        <v>78.75</v>
       </c>
       <c r="T19" s="12">
         <v>40</v>
@@ -1928,11 +1935,15 @@
       <c r="O21" s="12">
         <v>3</v>
       </c>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="13"/>
+      <c r="P21" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>2</v>
+      </c>
       <c r="R21" s="12">
         <f>(O21+P21)*Q21</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="T21" s="12">
         <v>20</v>
@@ -2010,7 +2021,7 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="12">
         <f>(O22+P21)*Q21</f>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="T22" s="12">
         <v>30</v>
@@ -2050,7 +2061,7 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="12">
         <f>(O23+P21)*Q21</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T23" s="12">
         <v>40</v>
@@ -2168,11 +2179,15 @@
       <c r="O25" s="12">
         <v>3</v>
       </c>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="13"/>
+      <c r="P25" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>2.65</v>
+      </c>
       <c r="R25" s="12">
         <f>(O25+P25)*Q25</f>
-        <v>0</v>
+        <v>103.35</v>
       </c>
       <c r="T25" s="12">
         <v>20</v>
@@ -2250,7 +2265,7 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="12">
         <f>(O26+P25)*Q25</f>
-        <v>0</v>
+        <v>108.64999999999999</v>
       </c>
       <c r="T26" s="12">
         <v>30</v>
@@ -2289,7 +2304,7 @@
       <c r="Q27" s="7"/>
       <c r="R27" s="12">
         <f>(O27+P25)*Q25</f>
-        <v>0</v>
+        <v>119.25</v>
       </c>
       <c r="T27" s="12">
         <v>40</v>
@@ -2406,11 +2421,15 @@
       <c r="O29" s="12">
         <v>3</v>
       </c>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="13"/>
+      <c r="P29" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>2.75</v>
+      </c>
       <c r="R29" s="12">
         <f>(O29+P29)*Q29</f>
-        <v>0</v>
+        <v>123.75</v>
       </c>
       <c r="T29" s="12">
         <v>20</v>
@@ -2477,7 +2496,7 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="12">
         <f>(O30+P29)*Q29</f>
-        <v>0</v>
+        <v>129.25</v>
       </c>
       <c r="T30" s="12">
         <v>30</v>
@@ -2522,7 +2541,7 @@
       <c r="Q31" s="7"/>
       <c r="R31" s="12">
         <f>(O31+P29)*Q29</f>
-        <v>0</v>
+        <v>140.25</v>
       </c>
       <c r="T31" s="12">
         <v>40</v>
@@ -2587,11 +2606,15 @@
       <c r="O33" s="12">
         <v>3</v>
       </c>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="13"/>
+      <c r="P33" s="2">
+        <v>52</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>3.5</v>
+      </c>
       <c r="R33" s="12">
         <f>(O33+P33)*Q33</f>
-        <v>0</v>
+        <v>192.5</v>
       </c>
       <c r="T33" s="12">
         <v>20</v>
@@ -2643,7 +2666,7 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="12">
         <f>(O34+P33)*Q33</f>
-        <v>0</v>
+        <v>199.5</v>
       </c>
       <c r="T34" s="12">
         <v>30</v>
@@ -2673,7 +2696,7 @@
       <c r="Q35" s="7"/>
       <c r="R35" s="12">
         <f>(O35+P33)*Q33</f>
-        <v>0</v>
+        <v>213.5</v>
       </c>
       <c r="T35" s="12">
         <v>40</v>
@@ -2739,11 +2762,15 @@
       <c r="O37" s="12">
         <v>3</v>
       </c>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="13"/>
+      <c r="P37" s="2">
+        <v>64</v>
+      </c>
+      <c r="Q37" s="13">
+        <v>4</v>
+      </c>
       <c r="R37" s="12">
         <f>(O37+P37)*Q37</f>
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="T37" s="12">
         <v>20</v>
@@ -2795,7 +2822,7 @@
       <c r="Q38" s="7"/>
       <c r="R38" s="12">
         <f>(O38+P37)*Q37</f>
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="T38" s="12">
         <v>30</v>
@@ -2839,7 +2866,7 @@
       <c r="Q39" s="7"/>
       <c r="R39" s="12">
         <f>(O39+P37)*Q37</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="T39" s="12">
         <v>40</v>
